--- a/data/trans_orig/IP16A06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>20787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13432</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>29430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44245</t>
+          <t>45094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61042</t>
+          <t>61731</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119513</t>
+          <t>119409</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>124705</t>
+          <t>124708</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136278</t>
+          <t>136200</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142716</t>
+          <t>142702</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>259255</t>
+          <t>259897</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>266769</t>
+          <t>266763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39661</t>
+          <t>39971</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>29508</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>34790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65668</t>
+          <t>66255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39433</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36855</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30080</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47180</t>
+          <t>48259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>179274</t>
+          <t>179389</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>186176</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>184212</t>
+          <t>184876</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>190761</t>
+          <t>190787</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>367557</t>
+          <t>367407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>375823</t>
+          <t>375844</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40919</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>55217</t>
+          <t>55014</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59045</t>
+          <t>59042</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>158630</t>
+          <t>158493</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>142523</t>
+          <t>143058</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>147533</t>
+          <t>147541</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>304363</t>
+          <t>304097</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309548</t>
+          <t>309554</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP16A06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2461</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3016</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11070</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9207</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8509</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>72,92%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>35</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1195</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3676</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1195</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3889</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18661</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15665</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18661</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>16180</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>32286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>791</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3180</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,8%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>32,81%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4357</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10836</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8447</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7812</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>67,19%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>593</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3142</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3347</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15833</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13314</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>15833</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13536</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29430</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,107 +2780,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>725</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>725</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3632</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2931</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25801</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>23105</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>87,1%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>25801</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>22894</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45094</t>
+          <t>44379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3128,102 +3128,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2718</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3286</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3098</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4747</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4059</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>39167</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>36388</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>25270</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>23206</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>22638</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>97,48%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>89,52%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>87,33%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>39167</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>36769</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>102</t>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61731</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7061</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>7719</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>140706</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>136858</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>142735</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>123262</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>119409</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>124708</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>119628</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>124709</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>140706</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>136200</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>259897</t>
+          <t>259418</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>266763</t>
+          <t>266614</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,107 +4045,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4020</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,29%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3673</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -4158,74 +4158,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18242</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15040</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14937</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>78,37%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>60</t>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39971</t>
+          <t>39983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4393,102 +4393,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3439</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3408</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3986</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -4501,74 +4501,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36687</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34237</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>32272</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29508</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>29539</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36687</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>34790</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>103</t>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66255</t>
+          <t>65785</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4731,107 +4731,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>691</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3688</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3497</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>15,59%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3478</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4844,72 +4844,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22967</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19942</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22967</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19970</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39456</t>
+          <t>39437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5074,107 +5074,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1454</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4890</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4319</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>17,35%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1454</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5192</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -5187,74 +5187,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23438</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20002</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20573</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>82,65%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>57</t>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5417,107 +5417,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3407</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3767</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>25,08%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3935</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -5530,72 +5530,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12940</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>12940</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>10180</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>29633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5873,47 +5873,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13142</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6216,47 +6216,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>33511</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6446,107 +6446,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>722</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>722</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3540</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3659</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2996</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -6559,72 +6559,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>26182</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>23227</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>86,33%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>26182</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>23364</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48259</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6794,67 +6794,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6824</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>7603</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6602</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -6902,72 +6902,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>188811</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>184654</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>190789</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>184045</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>179389</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>186176</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>179729</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>186194</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>98,42%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>188811</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>184876</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>190787</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>367407</t>
+          <t>367090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>375844</t>
+          <t>375839</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7368,107 +7368,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>626</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3240</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3123</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -7481,72 +7481,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23875</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21418</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23875</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21261</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>40635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>30413</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10287</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8510,47 +8510,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>34915</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8858,42 +8858,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>7779</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8971,52 +8971,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>7779</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>10580</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,107 +9426,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3922</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3887</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -9539,72 +9539,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13318</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>11125</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>79,67%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>13318</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>10042</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29790</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9769,72 +9769,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3061</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3939</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3683</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2990</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -9887,69 +9887,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>29679</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>27206</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>28153</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>25355</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>25611</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>96,1%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>86,55%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>29679</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>27277</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>90</t>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>55014</t>
+          <t>54795</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59042</t>
+          <t>59038</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,72 +10112,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4043</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>146266</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>142594</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>147536</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>161395</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>158493</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>158585</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>146266</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>143058</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>147541</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>304097</t>
+          <t>304219</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309554</t>
+          <t>309613</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
